--- a/Data_10536.XLSX
+++ b/Data_10536.XLSX
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Committee\Com-12140947\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git tracked\committeFormes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9816"/>
+    <workbookView xWindow="0" yWindow="450" windowWidth="21600" windowHeight="9810"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -638,29 +638,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="69.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="69.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,9 +688,6 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1">
-        <v>0</v>
-      </c>
       <c r="K1" t="s">
         <v>9</v>
       </c>
@@ -719,7 +716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -776,7 +773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -833,7 +830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -890,7 +887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>58</v>
       </c>
@@ -947,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>60</v>
       </c>
@@ -1004,7 +1001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -1061,7 +1058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -1118,7 +1115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1175,7 +1172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -1232,7 +1229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
